--- a/TP3/tabla_medias_2005.xlsx
+++ b/TP3/tabla_medias_2005.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -592,16 +592,32 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
+          <t>ad_equiv_hogar</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4.10856482907299</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.14704382183908</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.03847899276609024</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
           <t>intercept</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B12" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C12" t="n">
         <v>1</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D12" t="n">
         <v>0</v>
       </c>
     </row>
